--- a/Orçado/Orça-Seringal/COVOA - SERINGAL.xlsx
+++ b/Orçado/Orça-Seringal/COVOA - SERINGAL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\henrique.santos\orcamento2027\budgetflow-insights\Orçado\Orça-Seringal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39683BA3-1FBA-4648-B1F0-5D973F2B1133}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC6DE06A-F370-4EE9-A842-93FB0E4611B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20520" yWindow="1920" windowWidth="20640" windowHeight="11040" xr2:uid="{A12DF7AC-70C8-4C1A-B49B-45083BC63E48}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A12DF7AC-70C8-4C1A-B49B-45083BC63E48}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="100">
   <si>
     <t>4.1.01.01.0001</t>
   </si>
@@ -237,6 +237,108 @@
   </si>
   <si>
     <t>RATEIO TRATORES LEVES</t>
+  </si>
+  <si>
+    <t>RATEIO CARRETAS AGRICOLAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RATEIO CARRETAS AGRICOLAS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RATEIO CARRETAS TANQUE </t>
+  </si>
+  <si>
+    <t>RATEIO CONFRATERNIZACOES E EVENTOS COM COLABORADORES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RATEIO MEDICINA E SEGURANCA DO TRABALHO </t>
+  </si>
+  <si>
+    <t>RATEIO MOTOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RATEIO OFICINA </t>
+  </si>
+  <si>
+    <t>RATEIO OUTROS IMPLEMENTOS</t>
+  </si>
+  <si>
+    <t>RATEIO PÁ CARREGADEIRAS</t>
+  </si>
+  <si>
+    <t>RATEIO PROGRAMA INTEGRIDADE</t>
+  </si>
+  <si>
+    <t>RATEIO PROJETOS DESENVOLVIMENTO HUMANO</t>
+  </si>
+  <si>
+    <t>RATEIO PULVERIZADORES</t>
+  </si>
+  <si>
+    <t>RATEIO RECEBIDO</t>
+  </si>
+  <si>
+    <t>RATEIO SUPERVISAO SERINGUEIRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RATEIO TRATORES MEDIOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RATEIO VEICULOS LEVES </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RATEIO VEICULOS MEDIOS </t>
+  </si>
+  <si>
+    <t>4.2.01.02.0034</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0020</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0052</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0047</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0035</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0045</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0017</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0018</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0024</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0046</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0064</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0066</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0051</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0036</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0037</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0038</t>
+  </si>
+  <si>
+    <t>FRETES E CARRETOS PJ</t>
   </si>
 </sst>
 </file>
@@ -673,12 +775,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{688BEDFE-F848-4755-854B-AF0C5365EA53}">
-  <dimension ref="A1:O28"/>
+  <dimension ref="A1:O45"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="48.77734375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.5546875" customWidth="1"/>
-    <col min="3" max="3" width="38.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="58.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="15" width="10.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -878,7 +980,7 @@
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>99</v>
       </c>
       <c r="D5" s="4">
         <v>17305.02</v>
@@ -1846,47 +1948,588 @@
         <v>64</v>
       </c>
       <c r="B28" t="s">
+        <v>83</v>
+      </c>
+      <c r="C28" t="s">
+        <v>66</v>
+      </c>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4">
+        <v>375.56</v>
+      </c>
+      <c r="K28" s="4">
+        <v>375.56</v>
+      </c>
+      <c r="L28" s="4"/>
+      <c r="M28" s="4"/>
+      <c r="N28" s="4"/>
+      <c r="O28" s="4"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>64</v>
+      </c>
+      <c r="B29" t="s">
+        <v>83</v>
+      </c>
+      <c r="C29" t="s">
+        <v>67</v>
+      </c>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4">
+        <v>375.56</v>
+      </c>
+      <c r="H29" s="4">
+        <v>375.56</v>
+      </c>
+      <c r="I29" s="4">
+        <v>375.56</v>
+      </c>
+      <c r="J29" s="4"/>
+      <c r="K29" s="4"/>
+      <c r="L29" s="4"/>
+      <c r="M29" s="4"/>
+      <c r="N29" s="4"/>
+      <c r="O29" s="4"/>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>64</v>
+      </c>
+      <c r="B30" t="s">
+        <v>88</v>
+      </c>
+      <c r="C30" t="s">
+        <v>68</v>
+      </c>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4">
+        <v>96.64</v>
+      </c>
+      <c r="H30" s="4">
+        <v>100.9888</v>
+      </c>
+      <c r="I30" s="4">
+        <v>100.9888</v>
+      </c>
+      <c r="J30" s="4">
+        <v>100.9888</v>
+      </c>
+      <c r="K30" s="4">
+        <v>100.9888</v>
+      </c>
+      <c r="L30" s="4"/>
+      <c r="M30" s="4"/>
+      <c r="N30" s="4"/>
+      <c r="O30" s="4"/>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>64</v>
+      </c>
+      <c r="B31" t="s">
+        <v>89</v>
+      </c>
+      <c r="C31" t="s">
+        <v>69</v>
+      </c>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4">
+        <v>332.64000000000004</v>
+      </c>
+      <c r="H31" s="4">
+        <v>331.52</v>
+      </c>
+      <c r="I31" s="4">
+        <v>1830.6399999999999</v>
+      </c>
+      <c r="J31" s="4">
+        <v>229.04</v>
+      </c>
+      <c r="K31" s="4">
+        <v>74.48</v>
+      </c>
+      <c r="L31" s="4"/>
+      <c r="M31" s="4"/>
+      <c r="N31" s="4"/>
+      <c r="O31" s="4"/>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>64</v>
+      </c>
+      <c r="B32" t="s">
+        <v>90</v>
+      </c>
+      <c r="C32" t="s">
+        <v>70</v>
+      </c>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4">
+        <v>2563.02</v>
+      </c>
+      <c r="H32" s="4">
+        <v>2563.02</v>
+      </c>
+      <c r="I32" s="4">
+        <v>2563.02</v>
+      </c>
+      <c r="J32" s="4">
+        <v>2563.02</v>
+      </c>
+      <c r="K32" s="4">
+        <v>2563.02</v>
+      </c>
+      <c r="L32" s="4"/>
+      <c r="M32" s="4"/>
+      <c r="N32" s="4"/>
+      <c r="O32" s="4"/>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>64</v>
+      </c>
+      <c r="B33" t="s">
+        <v>84</v>
+      </c>
+      <c r="C33" t="s">
+        <v>71</v>
+      </c>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4">
+        <v>1008</v>
+      </c>
+      <c r="H33" s="4">
+        <v>1008</v>
+      </c>
+      <c r="I33" s="4">
+        <v>1008</v>
+      </c>
+      <c r="J33" s="4">
+        <v>1008</v>
+      </c>
+      <c r="K33" s="4">
+        <v>1008</v>
+      </c>
+      <c r="L33" s="4"/>
+      <c r="M33" s="4"/>
+      <c r="N33" s="4"/>
+      <c r="O33" s="4"/>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>64</v>
+      </c>
+      <c r="B34" t="s">
+        <v>91</v>
+      </c>
+      <c r="C34" t="s">
+        <v>72</v>
+      </c>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4">
+        <v>1127</v>
+      </c>
+      <c r="H34" s="4">
+        <v>1177.7149999999999</v>
+      </c>
+      <c r="I34" s="4">
+        <v>1177.7149999999999</v>
+      </c>
+      <c r="J34" s="4">
+        <v>1177.7149999999999</v>
+      </c>
+      <c r="K34" s="4">
+        <v>1177.7149999999999</v>
+      </c>
+      <c r="L34" s="4"/>
+      <c r="M34" s="4"/>
+      <c r="N34" s="4"/>
+      <c r="O34" s="4"/>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>64</v>
+      </c>
+      <c r="B35" t="s">
+        <v>85</v>
+      </c>
+      <c r="C35" t="s">
+        <v>73</v>
+      </c>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4">
+        <v>2590</v>
+      </c>
+      <c r="H35" s="4">
+        <v>2706.5499999999997</v>
+      </c>
+      <c r="I35" s="4">
+        <v>2706.5499999999997</v>
+      </c>
+      <c r="J35" s="4">
+        <v>2706.5499999999997</v>
+      </c>
+      <c r="K35" s="4">
+        <v>2706.5499999999997</v>
+      </c>
+      <c r="L35" s="4"/>
+      <c r="M35" s="4"/>
+      <c r="N35" s="4"/>
+      <c r="O35" s="4"/>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>64</v>
+      </c>
+      <c r="B36" t="s">
+        <v>92</v>
+      </c>
+      <c r="C36" t="s">
+        <v>74</v>
+      </c>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4">
+        <v>1487</v>
+      </c>
+      <c r="H36" s="4">
+        <v>1487</v>
+      </c>
+      <c r="I36" s="4">
+        <v>1487</v>
+      </c>
+      <c r="J36" s="4">
+        <v>1487</v>
+      </c>
+      <c r="K36" s="4">
+        <v>1487</v>
+      </c>
+      <c r="L36" s="4"/>
+      <c r="M36" s="4"/>
+      <c r="N36" s="4"/>
+      <c r="O36" s="4"/>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>64</v>
+      </c>
+      <c r="B37" t="s">
+        <v>93</v>
+      </c>
+      <c r="C37" t="s">
+        <v>75</v>
+      </c>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4">
+        <v>343</v>
+      </c>
+      <c r="H37" s="4">
+        <v>356.72</v>
+      </c>
+      <c r="I37" s="4">
+        <v>356.72</v>
+      </c>
+      <c r="J37" s="4">
+        <v>356.72</v>
+      </c>
+      <c r="K37" s="4">
+        <v>356.72</v>
+      </c>
+      <c r="L37" s="4"/>
+      <c r="M37" s="4"/>
+      <c r="N37" s="4"/>
+      <c r="O37" s="4"/>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>64</v>
+      </c>
+      <c r="B38" t="s">
+        <v>94</v>
+      </c>
+      <c r="C38" t="s">
+        <v>76</v>
+      </c>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4">
+        <v>453</v>
+      </c>
+      <c r="H38" s="4">
+        <v>453</v>
+      </c>
+      <c r="I38" s="4">
+        <v>453</v>
+      </c>
+      <c r="J38" s="4">
+        <v>453</v>
+      </c>
+      <c r="K38" s="4">
+        <v>453</v>
+      </c>
+      <c r="L38" s="4"/>
+      <c r="M38" s="4"/>
+      <c r="N38" s="4"/>
+      <c r="O38" s="4"/>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>64</v>
+      </c>
+      <c r="B39" t="s">
+        <v>86</v>
+      </c>
+      <c r="C39" t="s">
+        <v>77</v>
+      </c>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="4">
+        <v>522</v>
+      </c>
+      <c r="H39" s="4">
+        <v>91.6</v>
+      </c>
+      <c r="I39" s="4">
+        <v>48.696999999999996</v>
+      </c>
+      <c r="J39" s="4">
+        <v>103.455</v>
+      </c>
+      <c r="K39" s="4">
+        <v>136.89499999999998</v>
+      </c>
+      <c r="L39" s="4"/>
+      <c r="M39" s="4"/>
+      <c r="N39" s="4"/>
+      <c r="O39" s="4"/>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>64</v>
+      </c>
+      <c r="B40" t="s">
         <v>26</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C40" t="s">
+        <v>78</v>
+      </c>
+      <c r="D40" s="4">
+        <v>52477.872649614699</v>
+      </c>
+      <c r="E40" s="4">
+        <v>58704.077122881543</v>
+      </c>
+      <c r="F40" s="4">
+        <v>51523.411357903547</v>
+      </c>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="4"/>
+      <c r="L40" s="4">
+        <v>53143.003448078474</v>
+      </c>
+      <c r="M40" s="4">
+        <v>54204.483140297474</v>
+      </c>
+      <c r="N40" s="4">
+        <v>85004.277682968474</v>
+      </c>
+      <c r="O40" s="4">
+        <v>68055.414879987467</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>64</v>
+      </c>
+      <c r="B41" t="s">
+        <v>95</v>
+      </c>
+      <c r="C41" t="s">
+        <v>79</v>
+      </c>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4">
+        <v>8584.7710067113876</v>
+      </c>
+      <c r="H41" s="4">
+        <v>8974.3683370787894</v>
+      </c>
+      <c r="I41" s="4">
+        <v>9134.2846606213043</v>
+      </c>
+      <c r="J41" s="4">
+        <v>13133.591038621304</v>
+      </c>
+      <c r="K41" s="4">
+        <v>9358.9412086213051</v>
+      </c>
+      <c r="L41" s="4"/>
+      <c r="M41" s="4"/>
+      <c r="N41" s="4"/>
+      <c r="O41" s="4"/>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>64</v>
+      </c>
+      <c r="B42" t="s">
+        <v>87</v>
+      </c>
+      <c r="C42" t="s">
         <v>65</v>
       </c>
-      <c r="D28" s="4">
-        <v>48852.789006711377</v>
-      </c>
-      <c r="E28" s="4">
-        <v>54880.004137078773</v>
-      </c>
-      <c r="F28" s="4">
-        <v>56428.709470621296</v>
-      </c>
-      <c r="G28" s="4">
-        <v>61998.402578621302</v>
-      </c>
-      <c r="H28" s="4">
-        <v>57947.861978621295</v>
-      </c>
-      <c r="I28" s="4">
-        <v>53143.003448078474</v>
-      </c>
-      <c r="J28" s="4">
-        <v>54204.483140297474</v>
-      </c>
-      <c r="K28" s="4">
-        <v>85004.277682968474</v>
-      </c>
-      <c r="L28" s="4">
-        <v>68055.414879987467</v>
-      </c>
-      <c r="M28" s="4">
-        <v>52477.872649614699</v>
-      </c>
-      <c r="N28" s="4">
-        <v>58704.077122881543</v>
-      </c>
-      <c r="O28" s="4">
-        <v>51523.411357903547</v>
-      </c>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+      <c r="G42" s="4">
+        <v>9748.1579999999994</v>
+      </c>
+      <c r="H42" s="4">
+        <v>15375.191999999999</v>
+      </c>
+      <c r="I42" s="4">
+        <v>15307.764009999999</v>
+      </c>
+      <c r="J42" s="4">
+        <v>18424.992739999998</v>
+      </c>
+      <c r="K42" s="4">
+        <v>18270.221969999999</v>
+      </c>
+      <c r="L42" s="4"/>
+      <c r="M42" s="4"/>
+      <c r="N42" s="4"/>
+      <c r="O42" s="4"/>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>64</v>
+      </c>
+      <c r="B43" t="s">
+        <v>96</v>
+      </c>
+      <c r="C43" t="s">
+        <v>80</v>
+      </c>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="4">
+        <v>0</v>
+      </c>
+      <c r="H43" s="4">
+        <v>0</v>
+      </c>
+      <c r="I43" s="4">
+        <v>0</v>
+      </c>
+      <c r="J43" s="4">
+        <v>0</v>
+      </c>
+      <c r="K43" s="4">
+        <v>0</v>
+      </c>
+      <c r="L43" s="4"/>
+      <c r="M43" s="4"/>
+      <c r="N43" s="4"/>
+      <c r="O43" s="4"/>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>64</v>
+      </c>
+      <c r="B44" t="s">
+        <v>97</v>
+      </c>
+      <c r="C44" t="s">
+        <v>81</v>
+      </c>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="4">
+        <v>5706</v>
+      </c>
+      <c r="H44" s="4">
+        <v>5962.7699999999995</v>
+      </c>
+      <c r="I44" s="4">
+        <v>5962.7699999999995</v>
+      </c>
+      <c r="J44" s="4">
+        <v>5962.7699999999995</v>
+      </c>
+      <c r="K44" s="4">
+        <v>5962.7699999999995</v>
+      </c>
+      <c r="L44" s="4"/>
+      <c r="M44" s="4"/>
+      <c r="N44" s="4"/>
+      <c r="O44" s="4"/>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>64</v>
+      </c>
+      <c r="B45" t="s">
+        <v>98</v>
+      </c>
+      <c r="C45" t="s">
+        <v>82</v>
+      </c>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="4">
+        <v>13916</v>
+      </c>
+      <c r="H45" s="4">
+        <v>13916</v>
+      </c>
+      <c r="I45" s="4">
+        <v>13916</v>
+      </c>
+      <c r="J45" s="4">
+        <v>13916</v>
+      </c>
+      <c r="K45" s="4">
+        <v>13916</v>
+      </c>
+      <c r="L45" s="4"/>
+      <c r="M45" s="4"/>
+      <c r="N45" s="4"/>
+      <c r="O45" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
